--- a/Primer_Analisis_Cafe.xlsx
+++ b/Primer_Analisis_Cafe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailunicundiedu-my.sharepoint.com/personal/feliperamirez_ucundinamarca_edu_co/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailunicundiedu-my.sharepoint.com/personal/feliperamirez_ucundinamarca_edu_co/Documents/UN_AGRARIAS_CAFE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{D5361778-1024-4D12-8114-E2DFF167DD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74FD61E8-05D8-4165-A930-BD577EFBD7AB}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{D5361778-1024-4D12-8114-E2DFF167DD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B715FD3A-9E03-43AC-821D-6ACA27A0DF77}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AC8509AD-BB1F-428D-B155-1C622288DF87}"/>
+    <workbookView xWindow="13380" yWindow="0" windowWidth="10812" windowHeight="13776" xr2:uid="{AC8509AD-BB1F-428D-B155-1C622288DF87}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1624,7 +1624,7 @@
         <v>ELEGIDO VF</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
